--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +923,56 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>source.hsr-wiki.automaton-direwolf-complete.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Automaton_Direwolf_(Complete)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Exact public World 2 level-27 HP, ATK, DEF, SPD, EHR and Effect RES transcribed into committed Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4d4311796be765c1e2a223719ff4549ab663838a3fcbc051ea85e2e2a655909c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,6 +973,56 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>source.hsr-wiki.automaton-grizzly-complete.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Automaton_Grizzly_(Complete)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Exact public World 2 level-27 HP, ATK, DEF, SPD, EHR and Effect RES transcribed into committed Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0d1d5ed79c00fde7fbd0f40ae9906c1e809198a79a8e1c94fc51fa4ceb771829</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,6 +1023,56 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>source.hsr-db.blaze-out-of-space.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Database Wiki</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://starrail.honeyhunterworld.com/blaze-out-of-space-enemy-2/?lang=EN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Public level values and the exact retained hard-level curve inputs are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>453a98b3dec527ba611ccb4138e69af7686f68e72194479769300ac6e7963ef8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,6 +1073,56 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>source.hsr-wiki.cloud-knight-lieutenant-yanqing-complete.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Cloud_Knight_Lieutenant:_Yanqing_(Complete)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Exact public per-level values are committed with retained structured AI and ability source hashes.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>26675eafbb7481936c53e20fcc1a6ea7ae50a79452be337ed618da75fb7d753b</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,6 +1123,56 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>source.hsr-wiki.cocolia-complete.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Cocolia_(Complete)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Exact public per-level values are committed with retained structured AI and ability source hashes.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>c7e7d2b355406f348aca7e306725669a35231c556d4656553a567d58df4b0525</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1173,6 +1173,56 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>source.hsr-wiki.gepard-complete.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Gepard_(Complete)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Exact public per-level values are committed with retained structured AI and ability source hashes.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5d9b55cfcf3785dfa5ebdd490c94159a73152c1a7b606eb73fbe3d59701cdd8c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1223,6 +1223,56 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>source.hsr-wiki.ice-out-of-space.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Ice_Out_of_Space</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Exact public per-level values and mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2e12722a69ed4d9e3505ab976461a8ffff488882066dc5e110c2596108b120e4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,6 +1273,56 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>source.hsr-wiki.something-unto-death-complete.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Memory_Zone_Meme_%22Something_Unto_Death%22_%28Complete%29</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Exact public World 9 level values and capture mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>baf95718a79bf0cf1e26b72e6c8a96b3388435b5891293572c9ab7688610c37b</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1323,6 +1323,56 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>source.hsr-wiki.stellaron-hunter-kafka-complete.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Stellaron_Hunter:_Kafka_(Complete)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Exact World 5 levels and public Kafka mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0c1f380b815886649d1ed34a2008be533b7bcbf815f76697f200fe4d4ea0a978</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,6 +1373,56 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>source.hsr-wiki.svarog-complete.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Svarog_(Complete)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Exact World 4 levels and public Svarog mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>9dd5d4bd0d456367cb33a419d075adb6bc1803885288628edb5c0a1a700cd50a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1423,6 +1423,56 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>source.goal07.enemy-s12.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Abundance_Sprite%3A_Golden_Hound</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>30e9da848659c264b4cd88dbefb5184f6cef8dbcfb0da28b96366c8ff23dc2d8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1473,6 +1473,56 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>source.goal07.enemy-s13.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Automaton_Spider</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>b8ac0544918a16ec2aa1fdeb44710d56d34c440f6e7d7670a5ad5378b2980d60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,6 +1523,56 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>source.goal07.enemy-s14.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Entranced_Ingenium%3A_Illumination_Dragonfish</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7029ace9aa6d914df71837fcaf80b7835e391c3dc4bb3a7d6184cbcb0eb7c16d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,6 +1573,56 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>source.goal07.enemy-s15.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Mara-Struck_Soldier</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1c72ae67bc8824ec64eb8d32020d56ca828f8acae2965c1b142df2c40e9cac5b</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,6 +1623,56 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>source.goal07.enemy-s16.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Silvermane_Lieutenant</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>cfd5c01eaa2ea61c4794d090b3fc4a840ed303ebbdb98ce9134378227be4bcb7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1673,6 +1673,56 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>source.goal07.enemy-s17.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Voidranger%3A_Reaver</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>66e4eb362380a285caf0a06a360629ab8895fc6a30bd63e1a9dea34897edad82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1723,6 +1723,56 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>source.goal07.enemy-s18.2026-07-29</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://honkai-star-rail.fandom.com/wiki/Voidranger%3A_Trampler</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CommunityMaintained</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SecondaryVersionSensitiveCrossCheck</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fd4802d9930af4aaddb2a6a9d843574536cfea13ee2dc651fc3f304f571dba31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SourceRecord.xlsx
+++ b/config/data/SourceRecord.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SourceRecord" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceRecord" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,360 +499,384 @@
   </sheetPr>
   <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="12.7109375" customWidth="1" style="5" min="2" max="6"/>
+    <col width="23.7109375" customWidth="1" style="5" min="7" max="7"/>
+    <col width="20.7109375" customWidth="1" style="5" min="8" max="8"/>
+    <col width="16.7109375" customWidth="1" style="5" min="9" max="9"/>
+    <col width="12.7109375" customWidth="1" style="5" min="10" max="10"/>
+    <col width="15.7109375" customWidth="1" style="5" min="11" max="11"/>
+    <col width="16.7109375" customWidth="1" style="5" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>SourceRecord</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>17a3872379321fb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>0a37e4d23fe9dd0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>stable_key</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>accessed_on</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>applicable_game_version</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>usage_note</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>evidence_sha256</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>conflict_note</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>stable_key</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>accessed_on</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>applicable_game_version</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>usage_note</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>evidence_sha256</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>conflict_note</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>i32</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;SourceCategory&gt;</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;Confidence&gt;</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>optional&lt;string&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>key;range=1..2147483647</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>length=1..160</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>length=1..200</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>length=1..2048</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>length=10..10</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>length=1..1000</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>length=64..64</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -829,7 +938,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>source.mar-7th-star-rail-res.7b349e39ee0f6f3bf814567995829b99c95e7a93</t>
+          <t>source.mar-7th-star-rail-res.b95e75c7e1273d819d20c530c0b7e13a3ef19fb4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -844,7 +953,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -864,18 +973,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Public released-data transcription aid; raw cache remains local and uncommitted. Revision 7b349e39ee0f6f3bf814567995829b99c95e7a93.</t>
+          <t>Public released-data transcription aid; raw cache remains local and uncommitted. Revision b95e75c7e1273d819d20c530c0b7e13a3ef19fb4.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2f281182f2e81fb13831c5ef15c840055c486ca0ecef57f84dba5d6836af14b4</t>
+          <t>b08a246d99cb9ef4bdfcc9de637b741151bca855798459b4303a7a1b6a4e515e</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>3</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -924,8 +1035,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>4</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -974,8 +1087,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>5</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1024,8 +1139,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>6</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1074,12 +1191,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>7</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>source.hsr-wiki.cloud-knight-lieutenant-yanqing-complete.2026-07-29</t>
+          <t>source.hsr-wiki.gepard-complete.2026-07-29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1089,7 +1208,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Cloud_Knight_Lieutenant:_Yanqing_(Complete)</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Gepard_(Complete)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1119,17 +1238,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>26675eafbb7481936c53e20fcc1a6ea7ae50a79452be337ed618da75fb7d753b</t>
+          <t>5d9b55cfcf3785dfa5ebdd490c94159a73152c1a7b606eb73fbe3d59701cdd8c</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>8</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>source.hsr-wiki.cocolia-complete.2026-07-29</t>
+          <t>source.hsr-wiki.ice-out-of-space.2026-07-29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1139,7 +1260,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Cocolia_(Complete)</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Ice_Out_of_Space</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1164,22 +1285,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Exact public per-level values are committed with retained structured AI and ability source hashes.</t>
+          <t>Exact public per-level values and mechanics are committed as Goal 07 evidence.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>c7e7d2b355406f348aca7e306725669a35231c556d4656553a567d58df4b0525</t>
+          <t>2e12722a69ed4d9e3505ab976461a8ffff488882066dc5e110c2596108b120e4</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>9</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>source.hsr-wiki.gepard-complete.2026-07-29</t>
+          <t>source.hsr-wiki.something-unto-death-complete.2026-07-29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1189,7 +1312,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Gepard_(Complete)</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Memory_Zone_Meme_%22Something_Unto_Death%22_%28Complete%29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1214,22 +1337,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Exact public per-level values are committed with retained structured AI and ability source hashes.</t>
+          <t>Exact public World 9 level values and capture mechanics are committed as Goal 07 evidence.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5d9b55cfcf3785dfa5ebdd490c94159a73152c1a7b606eb73fbe3d59701cdd8c</t>
+          <t>baf95718a79bf0cf1e26b72e6c8a96b3388435b5891293572c9ab7688610c37b</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>10</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>source.hsr-wiki.ice-out-of-space.2026-07-29</t>
+          <t>source.hsr-wiki.stellaron-hunter-kafka-complete.2026-07-29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1239,7 +1364,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Ice_Out_of_Space</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Stellaron_Hunter:_Kafka_(Complete)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1264,22 +1389,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Exact public per-level values and mechanics are committed as Goal 07 evidence.</t>
+          <t>Exact World 5 levels and public Kafka mechanics are committed as Goal 07 evidence.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2e12722a69ed4d9e3505ab976461a8ffff488882066dc5e110c2596108b120e4</t>
+          <t>0c1f380b815886649d1ed34a2008be533b7bcbf815f76697f200fe4d4ea0a978</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>11</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>source.hsr-wiki.something-unto-death-complete.2026-07-29</t>
+          <t>source.hsr-wiki.svarog-complete.2026-07-29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1289,7 +1416,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Memory_Zone_Meme_%22Something_Unto_Death%22_%28Complete%29</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Svarog_(Complete)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1314,32 +1441,34 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Exact public World 9 level values and capture mechanics are committed as Goal 07 evidence.</t>
+          <t>Exact World 4 levels and public Svarog mechanics are committed as Goal 07 evidence.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>baf95718a79bf0cf1e26b72e6c8a96b3388435b5891293572c9ab7688610c37b</t>
+          <t>9dd5d4bd0d456367cb33a419d075adb6bc1803885288628edb5c0a1a700cd50a</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>12</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>source.hsr-wiki.stellaron-hunter-kafka-complete.2026-07-29</t>
+          <t>source.goal07.enemy-s12.2026-07-29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Honkai: Star Rail Wiki</t>
+          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Stellaron_Hunter:_Kafka_(Complete)</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Abundance_Sprite%3A_Golden_Hound</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1364,32 +1493,34 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Exact World 5 levels and public Kafka mechanics are committed as Goal 07 evidence.</t>
+          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0c1f380b815886649d1ed34a2008be533b7bcbf815f76697f200fe4d4ea0a978</t>
+          <t>30e9da848659c264b4cd88dbefb5184f6cef8dbcfb0da28b96366c8ff23dc2d8</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>13</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>source.hsr-wiki.svarog-complete.2026-07-29</t>
+          <t>source.goal07.enemy-s13.2026-07-29</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Honkai: Star Rail Wiki</t>
+          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Svarog_(Complete)</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Automaton_Spider</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1414,22 +1545,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Exact World 4 levels and public Svarog mechanics are committed as Goal 07 evidence.</t>
+          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>9dd5d4bd0d456367cb33a419d075adb6bc1803885288628edb5c0a1a700cd50a</t>
+          <t>b8ac0544918a16ec2aa1fdeb44710d56d34c440f6e7d7670a5ad5378b2980d60</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>14</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>source.goal07.enemy-s12.2026-07-29</t>
+          <t>source.goal07.enemy-s14.2026-07-29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1439,7 +1572,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Abundance_Sprite%3A_Golden_Hound</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Entranced_Ingenium%3A_Illumination_Dragonfish</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1469,17 +1602,19 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30e9da848659c264b4cd88dbefb5184f6cef8dbcfb0da28b96366c8ff23dc2d8</t>
+          <t>7029ace9aa6d914df71837fcaf80b7835e391c3dc4bb3a7d6184cbcb0eb7c16d</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>15</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>source.goal07.enemy-s13.2026-07-29</t>
+          <t>source.goal07.enemy-s15.2026-07-29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1489,7 +1624,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Automaton_Spider</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Mara-Struck_Soldier</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1519,17 +1654,19 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>b8ac0544918a16ec2aa1fdeb44710d56d34c440f6e7d7670a5ad5378b2980d60</t>
+          <t>1c72ae67bc8824ec64eb8d32020d56ca828f8acae2965c1b142df2c40e9cac5b</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>16</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>source.goal07.enemy-s14.2026-07-29</t>
+          <t>source.goal07.enemy-s16.2026-07-29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1539,7 +1676,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Entranced_Ingenium%3A_Illumination_Dragonfish</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Silvermane_Lieutenant</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1569,17 +1706,19 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7029ace9aa6d914df71837fcaf80b7835e391c3dc4bb3a7d6184cbcb0eb7c16d</t>
+          <t>cfd5c01eaa2ea61c4794d090b3fc4a840ed303ebbdb98ce9134378227be4bcb7</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>17</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>source.goal07.enemy-s15.2026-07-29</t>
+          <t>source.goal07.enemy-s18.2026-07-29</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1589,7 +1728,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Mara-Struck_Soldier</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Voidranger%3A_Trampler</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1619,27 +1758,27 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1c72ae67bc8824ec64eb8d32020d56ca828f8acae2965c1b142df2c40e9cac5b</t>
+          <t>fd4802d9930af4aaddb2a6a9d843574536cfea13ee2dc651fc3f304f571dba31</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>source.goal07.enemy-s16.2026-07-29</t>
+          <t>source.hsr-wiki.cloud-knight-lieutenant-yanqing-complete.2026-07-29</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
+          <t>Honkai: Star Rail Wiki</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Silvermane_Lieutenant</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Cloud_Knight_Lieutenant:_Yanqing_(Complete)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1664,12 +1803,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
+          <t>Exact public per-level values are committed with retained structured AI and ability source hashes.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>cfd5c01eaa2ea61c4794d090b3fc4a840ed303ebbdb98ce9134378227be4bcb7</t>
+          <t>26675eafbb7481936c53e20fcc1a6ea7ae50a79452be337ed618da75fb7d753b</t>
         </is>
       </c>
     </row>
@@ -1725,21 +1864,21 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>source.goal07.enemy-s18.2026-07-29</t>
+          <t>source.hsr-wiki.cocolia-complete.2026-07-29</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Honkai: Star Rail Wiki and committed version 4.4 extraction</t>
+          <t>Honkai: Star Rail Wiki</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://honkai-star-rail.fandom.com/wiki/Voidranger%3A_Trampler</t>
+          <t>https://honkai-star-rail.fandom.com/wiki/Cocolia_(Complete)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1764,16 +1903,28 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Per-variant exact or approved derived level values and version 4.4 mechanics are committed as Goal 07 evidence.</t>
+          <t>Exact public per-level values are committed with retained structured AI and ability source hashes.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fd4802d9930af4aaddb2a6a9d843574536cfea13ee2dc651fc3f304f571dba31</t>
+          <t>c7e7d2b355406f348aca7e306725669a35231c556d4656553a567d58df4b0525</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: OfficialPublic, ProjectObservation, CommunityMaintained, StructuredTranscription, ProjectPolicy, SyntheticFixture" promptTitle="SourceCategory enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"OfficialPublic,ProjectObservation,CommunityMaintained,StructuredTranscription,ProjectPolicy,SyntheticFixture"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: OfficialVersionAndReleaseBoundary, PreparedExactStructured, SecondaryVersionSensitiveCrossCheck, PreparedContractPendingExecutableGolden, ReleasedTextBoundApproximation, Observed, ProjectPolicy, SyntheticFixture" promptTitle="Confidence enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"OfficialVersionAndReleaseBoundary,PreparedExactStructured,SecondaryVersionSensitiveCrossCheck,PreparedContractPendingExecutableGolden,ReleasedTextBoundApproximation,Observed,ProjectPolicy,SyntheticFixture"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>